--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AC2189-2FBC-954C-89A6-A430ED1F9804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EC16B2-A962-C144-BFF1-18765AF4DB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -17059,13 +17059,66 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>어둑시니: 강찬
-소문: 신주협</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>어둑시니</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>강찬</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>소문</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>신주협</t>
         </r>
       </text>
     </comment>
@@ -17887,12 +17940,712 @@
         </r>
       </text>
     </comment>
+    <comment ref="I795" authorId="0" shapeId="0" xr:uid="{01698E05-306B-F040-9716-2773D59BCDF9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>키키</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>최태이</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>호스트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>란</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>한유란</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>호스트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>욱</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>황인욱</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>호스트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김나연</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>호스트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김성현</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>호스트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>윤지우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>밴드</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>호스트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>피</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아노</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정지연</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>호스트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>기</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>타</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>손석만</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>호스트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>베</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>황현무</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>호스트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>퍼</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>커션</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>박진휘</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>호스트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>바</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이올린</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김요한</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11914" uniqueCount="4647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11929" uniqueCount="4660">
   <si>
     <t>시즌</t>
   </si>
@@ -31833,6 +32586,45 @@
   </si>
   <si>
     <t>김태환(오), 김채율, 한승렬</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1SA3U9blsx745Wqiwlx5URzj8V4qYBCRy/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1GJFlNhV4Ro5X8Y2BoNPVnDbRJQMz1Nny/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1DN4MKz9LzxHRg3owpg8EjZOoXi1_blCq/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1oaweuZKPI8nm_C20Knl2KPkyVpRCnlNY/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1e9oi_s96Rw2zb36k95QyX4uvQNImj2nz/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1cxPCRvODYv62ZnlW8BJXJkR-v37ZpbYt/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>키키의 경계성 인격장애 다이어리</t>
+  </si>
+  <si>
+    <t>최태이, 한유란, 황인욱, 김나연, 김성현, 윤지우</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ASVCl3ZJtT0TBnTVVkenEVh5dibI8Q4d/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ZyafU65GdtXIUDjN05RraFNc_VGzAJlE/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224396567271</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.xeddof1ei9j1</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/302950</t>
   </si>
 </sst>
 </file>
@@ -32064,7 +32856,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -32254,6 +33046,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -33196,7 +34018,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S794" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S795" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -33523,7 +34345,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V794"/>
+  <dimension ref="A1:V795"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -76284,7 +77106,7 @@
         <v>4258</v>
       </c>
       <c r="M701" s="15" t="s">
-        <v>14</v>
+        <v>4647</v>
       </c>
       <c r="N701" s="15" t="s">
         <v>14</v>
@@ -76768,7 +77590,7 @@
         <v>3313</v>
       </c>
       <c r="M709" s="15" t="s">
-        <v>14</v>
+        <v>4648</v>
       </c>
       <c r="N709" s="15" t="s">
         <v>14</v>
@@ -79069,10 +79891,10 @@
         <v>4246</v>
       </c>
       <c r="M748" s="52" t="s">
-        <v>14</v>
+        <v>4649</v>
       </c>
       <c r="N748" s="52" t="s">
-        <v>14</v>
+        <v>4650</v>
       </c>
       <c r="O748" s="51" t="s">
         <v>4247</v>
@@ -79187,7 +80009,7 @@
         <v>4268</v>
       </c>
       <c r="M750" s="52" t="s">
-        <v>14</v>
+        <v>4651</v>
       </c>
       <c r="N750" s="52" t="s">
         <v>14</v>
@@ -81193,7 +82015,7 @@
         <v>4430</v>
       </c>
       <c r="M784" s="52" t="s">
-        <v>14</v>
+        <v>4652</v>
       </c>
       <c r="N784" s="52" t="s">
         <v>14</v>
@@ -81802,6 +82624,65 @@
       </c>
       <c r="S794" s="47" t="s">
         <v>3410</v>
+      </c>
+    </row>
+    <row r="795" spans="1:19" ht="17" customHeight="1">
+      <c r="A795" s="64">
+        <v>794</v>
+      </c>
+      <c r="B795" s="65">
+        <v>46265</v>
+      </c>
+      <c r="C795" s="66">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D795" s="67" t="s">
+        <v>346</v>
+      </c>
+      <c r="E795" s="67" t="s">
+        <v>41</v>
+      </c>
+      <c r="F795" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="G795" s="68" t="s">
+        <v>4653</v>
+      </c>
+      <c r="H795" s="67" t="s">
+        <v>357</v>
+      </c>
+      <c r="I795" s="69" t="s">
+        <v>4654</v>
+      </c>
+      <c r="J795" s="70">
+        <v>0</v>
+      </c>
+      <c r="K795" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="L795" s="72" t="s">
+        <v>4655</v>
+      </c>
+      <c r="M795" s="52" t="s">
+        <v>4656</v>
+      </c>
+      <c r="N795" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O795" s="72" t="s">
+        <v>4657</v>
+      </c>
+      <c r="P795" s="72" t="s">
+        <v>4658</v>
+      </c>
+      <c r="Q795" s="72" t="s">
+        <v>4659</v>
+      </c>
+      <c r="R795" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="S795" s="73" t="s">
+        <v>3408</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EC16B2-A962-C144-BFF1-18765AF4DB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00340668-F25D-1B42-9FA6-CEBAA7E6644F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
+    <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -18640,12 +18640,155 @@
         </r>
       </text>
     </comment>
+    <comment ref="I796" authorId="0" shapeId="0" xr:uid="{AFD3EE91-2134-6C45-BF06-697F4B9B1952}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Orpheus: REEVE CARNEY
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Hermes: ANDRÉ DE SHIELDS
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Persephone: AMBER GRAY
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Eurydice: EVA NOBLEZADA
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Hades: PATRICK PAGE
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Fates:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">BELLA BROWN, MADELINE CHARLEMAGNE, ALLIE DANIEL
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Workers:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">LAUREN AZANIA, TIAGO DHONDT-BAMBERGER, RYESHA HIGGS, WAYLON JACOBS, CHRISTOPHER SHORT
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Swings:
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>LUCINDA BUCKLEY, FRANCESSCA DANIELLA-BAKER, WINNY HERBERT, MIRIAM NYARKO</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11929" uniqueCount="4660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11944" uniqueCount="4668">
   <si>
     <t>시즌</t>
   </si>
@@ -32625,6 +32768,30 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/302950</t>
+  </si>
+  <si>
+    <t>라센 25</t>
+  </si>
+  <si>
+    <t>Reeve Carney, André Shields, Amber Gray, Eva Noblezada, Patrick Page, Bella Brown, Madeline Charlemagne, Allie Daniel</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Ye8DqD_xG7s4vFiwzqkdXCdKMLA6HBdx/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TF2gkpPXTv1JjR1b3DmrAFR5DY7o0Fju/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1UzZUcTv8LmCCmDihx51wedf_N3A74pzI/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224398766861</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.tb5l0y4lxe5e</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Hadestown-Musical-Brett-Sullivan/dp/B0H9RRSCB9</t>
   </si>
 </sst>
 </file>
@@ -32856,7 +33023,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -33046,36 +33213,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -34018,7 +34155,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S795" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S796" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -34345,7 +34482,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V795"/>
+  <dimension ref="A1:V796"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -82627,40 +82764,40 @@
       </c>
     </row>
     <row r="795" spans="1:19" ht="17" customHeight="1">
-      <c r="A795" s="64">
+      <c r="A795" s="59">
         <v>794</v>
       </c>
-      <c r="B795" s="65">
+      <c r="B795" s="60">
         <v>46265</v>
       </c>
-      <c r="C795" s="66">
+      <c r="C795" s="61">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D795" s="67" t="s">
+      <c r="D795" s="59" t="s">
         <v>346</v>
       </c>
-      <c r="E795" s="67" t="s">
+      <c r="E795" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="F795" s="67" t="s">
+      <c r="F795" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="G795" s="68" t="s">
+      <c r="G795" s="62" t="s">
         <v>4653</v>
       </c>
-      <c r="H795" s="67" t="s">
+      <c r="H795" s="59" t="s">
         <v>357</v>
       </c>
-      <c r="I795" s="69" t="s">
+      <c r="I795" s="63" t="s">
         <v>4654</v>
       </c>
-      <c r="J795" s="70">
+      <c r="J795" s="54">
         <v>0</v>
       </c>
-      <c r="K795" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="L795" s="72" t="s">
+      <c r="K795" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="L795" s="51" t="s">
         <v>4655</v>
       </c>
       <c r="M795" s="52" t="s">
@@ -82669,20 +82806,79 @@
       <c r="N795" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="O795" s="72" t="s">
+      <c r="O795" s="51" t="s">
         <v>4657</v>
       </c>
-      <c r="P795" s="72" t="s">
+      <c r="P795" s="51" t="s">
         <v>4658</v>
       </c>
-      <c r="Q795" s="72" t="s">
+      <c r="Q795" s="51" t="s">
         <v>4659</v>
       </c>
-      <c r="R795" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="S795" s="73" t="s">
+      <c r="R795" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="S795" s="47" t="s">
         <v>3408</v>
+      </c>
+    </row>
+    <row r="796" spans="1:19" ht="17" customHeight="1">
+      <c r="A796" s="59">
+        <v>795</v>
+      </c>
+      <c r="B796" s="60">
+        <v>46267</v>
+      </c>
+      <c r="C796" s="61">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D796" s="59" t="s">
+        <v>14</v>
+      </c>
+      <c r="E796" s="59" t="s">
+        <v>4660</v>
+      </c>
+      <c r="F796" s="59" t="s">
+        <v>77</v>
+      </c>
+      <c r="G796" s="62" t="s">
+        <v>276</v>
+      </c>
+      <c r="H796" s="59" t="s">
+        <v>3471</v>
+      </c>
+      <c r="I796" s="63" t="s">
+        <v>4661</v>
+      </c>
+      <c r="J796" s="54">
+        <v>34244</v>
+      </c>
+      <c r="K796" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="L796" s="51" t="s">
+        <v>4662</v>
+      </c>
+      <c r="M796" s="52" t="s">
+        <v>4663</v>
+      </c>
+      <c r="N796" s="52" t="s">
+        <v>4664</v>
+      </c>
+      <c r="O796" s="51" t="s">
+        <v>4665</v>
+      </c>
+      <c r="P796" s="51" t="s">
+        <v>4666</v>
+      </c>
+      <c r="Q796" s="51" t="s">
+        <v>4667</v>
+      </c>
+      <c r="R796" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="S796" s="47" t="s">
+        <v>3411</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAD2357-62EC-A247-9733-21FAB71AACE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{047DD0D9-D2E4-4B49-AA3A-F0B01D810CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
+    <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -19303,13 +19303,174 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>스탠리(앨런, 레이건, 대니, 에이달라나, 아서, 케빈): 이재균
-윌버: 김정민</t>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>스탠리</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>앨런</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>레이건</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>대니</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>에이달라나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아서</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">, </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>케빈</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">): </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이재균</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>윌버</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김정민</t>
         </r>
       </text>
     </comment>
@@ -20215,6 +20376,222 @@
             <family val="2"/>
           </rPr>
           <t>신준석</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I802" authorId="0" shapeId="0" xr:uid="{3C340521-F5B2-FA4E-A9D4-D32E3754ED1A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>톰: 전성우
+소피/이자벨라: 이정화(넥)
+마이크 외: 곽다인
+엠마 외: 강은나
+멀티 연주자: 김치영
+퍼커셔니스트: 이우림</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I803" authorId="0" shapeId="0" xr:uid="{BB92D814-B82B-2042-A408-0D1003FF4E9A}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>레오</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김준우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주이진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루퍼트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>서동근</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>케넷</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이주원</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>데이지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>장수지</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I804" authorId="0" shapeId="0" xr:uid="{E8CA4037-12A8-D845-B630-A15E2DAC5C34}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>레오: 신수진
+아트: 백민서
+루퍼트: 임지수(로)
+케넷: 이주원
+데이지: 장수지</t>
         </r>
       </text>
     </comment>
@@ -20223,7 +20600,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12019" uniqueCount="4697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12064" uniqueCount="4711">
   <si>
     <t>시즌</t>
   </si>
@@ -34314,6 +34691,48 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.7dhhksg588eb</t>
+  </si>
+  <si>
+    <t>네이처 오브 포겟팅</t>
+  </si>
+  <si>
+    <t>전성우, 이정화(넥), 곽다인, 강은나</t>
+  </si>
+  <si>
+    <t>로프</t>
+  </si>
+  <si>
+    <t>김준우, 주이진, 서동근, 이주원, 장수지</t>
+  </si>
+  <si>
+    <t>신수진, 백민서, 임지수(로), 이주원, 장수지</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/12wM1xYosEWUyPq0Ri6EH1oKgzbvbSdjc/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224422089366</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.enj1syqjegy8</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1r-fhzHC9DVFRpE2ZLReVXGs7zK9O_Xga/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224422090636</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.orgwf4w457w</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/17-Sj3ppM3R3lVS3qpbcErwbwyutfuYq3/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224422092616</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.b95fjkb7v5pw</t>
   </si>
 </sst>
 </file>
@@ -34456,7 +34875,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -34540,12 +34959,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="6" tint="0.59996337778862885"/>
+      </left>
+      <right style="thin">
+        <color theme="6" tint="0.59996337778862885"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -34735,6 +35165,39 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -35707,7 +36170,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S801" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S804" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -36034,7 +36497,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V801"/>
+  <dimension ref="A1:V804"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -84670,40 +85133,40 @@
       </c>
     </row>
     <row r="801" spans="1:19" ht="17" customHeight="1">
-      <c r="A801" s="64">
+      <c r="A801" s="59">
         <v>800</v>
       </c>
-      <c r="B801" s="65">
+      <c r="B801" s="60">
         <v>46281</v>
       </c>
-      <c r="C801" s="66">
+      <c r="C801" s="61">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D801" s="67" t="s">
+      <c r="D801" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="E801" s="67" t="s">
+      <c r="E801" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="F801" s="67" t="s">
+      <c r="F801" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="G801" s="68" t="s">
+      <c r="G801" s="62" t="s">
         <v>4692</v>
       </c>
-      <c r="H801" s="67" t="s">
+      <c r="H801" s="59" t="s">
         <v>357</v>
       </c>
-      <c r="I801" s="69" t="s">
+      <c r="I801" s="63" t="s">
         <v>4693</v>
       </c>
-      <c r="J801" s="70">
+      <c r="J801" s="54">
         <v>16000</v>
       </c>
-      <c r="K801" s="71" t="s">
+      <c r="K801" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="L801" s="72" t="s">
+      <c r="L801" s="51" t="s">
         <v>4694</v>
       </c>
       <c r="M801" s="52" t="s">
@@ -84712,20 +85175,197 @@
       <c r="N801" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="O801" s="72" t="s">
+      <c r="O801" s="51" t="s">
         <v>4695</v>
       </c>
-      <c r="P801" s="72" t="s">
+      <c r="P801" s="51" t="s">
         <v>4696</v>
       </c>
-      <c r="Q801" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="R801" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="S801" s="73" t="s">
+      <c r="Q801" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="R801" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="S801" s="47" t="s">
         <v>3412</v>
+      </c>
+    </row>
+    <row r="802" spans="1:19" ht="17" customHeight="1">
+      <c r="A802" s="64">
+        <v>801</v>
+      </c>
+      <c r="B802" s="65">
+        <v>46287</v>
+      </c>
+      <c r="C802" s="66">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D802" s="67" t="s">
+        <v>174</v>
+      </c>
+      <c r="E802" s="67" t="s">
+        <v>54</v>
+      </c>
+      <c r="F802" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="G802" s="68" t="s">
+        <v>4697</v>
+      </c>
+      <c r="H802" s="67" t="s">
+        <v>357</v>
+      </c>
+      <c r="I802" s="69" t="s">
+        <v>4698</v>
+      </c>
+      <c r="J802" s="70">
+        <v>24000</v>
+      </c>
+      <c r="K802" s="71" t="s">
+        <v>184</v>
+      </c>
+      <c r="L802" s="72" t="s">
+        <v>4702</v>
+      </c>
+      <c r="M802" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N802" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O802" s="72" t="s">
+        <v>4703</v>
+      </c>
+      <c r="P802" s="72" t="s">
+        <v>4704</v>
+      </c>
+      <c r="Q802" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="R802" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="S802" s="74" t="s">
+        <v>3408</v>
+      </c>
+    </row>
+    <row r="803" spans="1:19" ht="17" customHeight="1">
+      <c r="A803" s="64">
+        <v>802</v>
+      </c>
+      <c r="B803" s="65">
+        <v>46288</v>
+      </c>
+      <c r="C803" s="66">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D803" s="67" t="s">
+        <v>4280</v>
+      </c>
+      <c r="E803" s="67" t="s">
+        <v>29</v>
+      </c>
+      <c r="F803" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="G803" s="68" t="s">
+        <v>4699</v>
+      </c>
+      <c r="H803" s="67" t="s">
+        <v>357</v>
+      </c>
+      <c r="I803" s="69" t="s">
+        <v>4700</v>
+      </c>
+      <c r="J803" s="70">
+        <v>25000</v>
+      </c>
+      <c r="K803" s="71" t="s">
+        <v>4282</v>
+      </c>
+      <c r="L803" s="72" t="s">
+        <v>4705</v>
+      </c>
+      <c r="M803" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N803" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="O803" s="72" t="s">
+        <v>4706</v>
+      </c>
+      <c r="P803" s="72" t="s">
+        <v>4707</v>
+      </c>
+      <c r="Q803" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="R803" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="S803" s="74" t="s">
+        <v>3412</v>
+      </c>
+    </row>
+    <row r="804" spans="1:19" ht="17" customHeight="1">
+      <c r="A804" s="75">
+        <v>803</v>
+      </c>
+      <c r="B804" s="76">
+        <v>46289</v>
+      </c>
+      <c r="C804" s="77">
+        <v>0.625</v>
+      </c>
+      <c r="D804" s="78" t="s">
+        <v>4280</v>
+      </c>
+      <c r="E804" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="F804" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="G804" s="79" t="s">
+        <v>4699</v>
+      </c>
+      <c r="H804" s="78" t="s">
+        <v>358</v>
+      </c>
+      <c r="I804" s="80" t="s">
+        <v>4701</v>
+      </c>
+      <c r="J804" s="81">
+        <v>24000</v>
+      </c>
+      <c r="K804" s="82" t="s">
+        <v>4282</v>
+      </c>
+      <c r="L804" s="83" t="s">
+        <v>4708</v>
+      </c>
+      <c r="M804" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="N804" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="O804" s="83" t="s">
+        <v>4709</v>
+      </c>
+      <c r="P804" s="83" t="s">
+        <v>4710</v>
+      </c>
+      <c r="Q804" s="83" t="s">
+        <v>14</v>
+      </c>
+      <c r="R804" s="83" t="s">
+        <v>14</v>
+      </c>
+      <c r="S804" s="84" t="s">
+        <v>3408</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAE8844-A2C7-CE45-B270-7D3AFC99C136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4059DF06-9C2E-7742-A6F7-CC4AB99F6742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18327,12 +18327,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="I806" authorId="0" shapeId="0" xr:uid="{69A01F92-1D66-694F-99F7-218FA1E322F5}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>레오 엘러튼: 우지한
+아트 레이놀즈: 주이진
+루퍼트 카델: 지상윤
+케넷 라글란: 정이운
+데이지 아든: 김한나</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12079" uniqueCount="4716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12094" uniqueCount="4720">
   <si>
     <t>시즌</t>
   </si>
@@ -32480,6 +32498,18 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.vhzpt7skry7e</t>
+  </si>
+  <si>
+    <t>우지한, 주이진, 지상윤, 정이운, 김한나</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1XSdZBoCN3L_TLz3rdc2kBK2XdaXIILId/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224429584279</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.cj5hsxzcmqx6</t>
   </si>
 </sst>
 </file>
@@ -32722,7 +32752,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -32915,6 +32945,36 @@
     </xf>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -33857,7 +33917,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S805" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S806" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -34184,7 +34244,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V805"/>
+  <dimension ref="A1:V806"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -83114,6 +83174,65 @@
         <v>3411</v>
       </c>
     </row>
+    <row r="806" spans="1:19" ht="17" customHeight="1">
+      <c r="A806" s="65">
+        <v>805</v>
+      </c>
+      <c r="B806" s="66">
+        <v>46296</v>
+      </c>
+      <c r="C806" s="67">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D806" s="68" t="s">
+        <v>4280</v>
+      </c>
+      <c r="E806" s="68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F806" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G806" s="69" t="s">
+        <v>4699</v>
+      </c>
+      <c r="H806" s="68" t="s">
+        <v>359</v>
+      </c>
+      <c r="I806" s="70" t="s">
+        <v>4716</v>
+      </c>
+      <c r="J806" s="71">
+        <v>18500</v>
+      </c>
+      <c r="K806" s="72" t="s">
+        <v>4282</v>
+      </c>
+      <c r="L806" s="73" t="s">
+        <v>4717</v>
+      </c>
+      <c r="M806" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="N806" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O806" s="73" t="s">
+        <v>4718</v>
+      </c>
+      <c r="P806" s="73" t="s">
+        <v>4719</v>
+      </c>
+      <c r="Q806" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R806" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="S806" s="74" t="s">
+        <v>3410</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4059DF06-9C2E-7742-A6F7-CC4AB99F6742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3168B291-61BF-5047-BCFD-11BC1F341B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18345,12 +18345,456 @@
         </r>
       </text>
     </comment>
+    <comment ref="I807" authorId="0" shapeId="0" xr:uid="{59DC3AF1-0B04-EE4C-919E-4B37D3EF21BF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>레오</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>엘러튼</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김준우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>레이놀즈</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주이진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루퍼트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>카델</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>지상윤</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>케넷</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>라글란</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>이주원</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>데이지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아든</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김한나</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>크스콜</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>레오</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주이진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>크스콜</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김준우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>크스콜</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루퍼트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>지상윤</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12094" uniqueCount="4720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12109" uniqueCount="4725">
   <si>
     <t>시즌</t>
   </si>
@@ -32510,6 +32954,21 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.cj5hsxzcmqx6</t>
+  </si>
+  <si>
+    <t>김준우, 주이진, 지상윤, 이주원, 김한나</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1SaaYWeQ9_jb1Qf2lwCOh5Ox2Qhnv5urk/view?usp=sharing</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224431213387</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.qiq9z4o9oz64</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/305585</t>
   </si>
 </sst>
 </file>
@@ -33917,7 +34376,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S806" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S807" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -34244,7 +34703,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V806"/>
+  <dimension ref="A1:V807"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -83175,40 +83634,40 @@
       </c>
     </row>
     <row r="806" spans="1:19" ht="17" customHeight="1">
-      <c r="A806" s="65">
+      <c r="A806" s="59">
         <v>805</v>
       </c>
-      <c r="B806" s="66">
+      <c r="B806" s="60">
         <v>46296</v>
       </c>
-      <c r="C806" s="67">
+      <c r="C806" s="61">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D806" s="68" t="s">
+      <c r="D806" s="59" t="s">
         <v>4280</v>
       </c>
-      <c r="E806" s="68" t="s">
+      <c r="E806" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="F806" s="68" t="s">
+      <c r="F806" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="G806" s="69" t="s">
+      <c r="G806" s="62" t="s">
         <v>4699</v>
       </c>
-      <c r="H806" s="68" t="s">
+      <c r="H806" s="59" t="s">
         <v>359</v>
       </c>
-      <c r="I806" s="70" t="s">
+      <c r="I806" s="63" t="s">
         <v>4716</v>
       </c>
-      <c r="J806" s="71">
+      <c r="J806" s="54">
         <v>18500</v>
       </c>
-      <c r="K806" s="72" t="s">
+      <c r="K806" s="50" t="s">
         <v>4282</v>
       </c>
-      <c r="L806" s="73" t="s">
+      <c r="L806" s="51" t="s">
         <v>4717</v>
       </c>
       <c r="M806" s="52" t="s">
@@ -83217,19 +83676,78 @@
       <c r="N806" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="O806" s="73" t="s">
+      <c r="O806" s="51" t="s">
         <v>4718</v>
       </c>
-      <c r="P806" s="73" t="s">
+      <c r="P806" s="51" t="s">
         <v>4719</v>
       </c>
-      <c r="Q806" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R806" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="S806" s="74" t="s">
+      <c r="Q806" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="R806" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="S806" s="47" t="s">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="807" spans="1:19" ht="17" customHeight="1">
+      <c r="A807" s="65">
+        <v>806</v>
+      </c>
+      <c r="B807" s="66">
+        <v>46298</v>
+      </c>
+      <c r="C807" s="67">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D807" s="68" t="s">
+        <v>4280</v>
+      </c>
+      <c r="E807" s="68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F807" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G807" s="69" t="s">
+        <v>4699</v>
+      </c>
+      <c r="H807" s="68" t="s">
+        <v>360</v>
+      </c>
+      <c r="I807" s="70" t="s">
+        <v>4720</v>
+      </c>
+      <c r="J807" s="71">
+        <v>27500</v>
+      </c>
+      <c r="K807" s="72" t="s">
+        <v>4282</v>
+      </c>
+      <c r="L807" s="73" t="s">
+        <v>4721</v>
+      </c>
+      <c r="M807" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="N807" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O807" s="73" t="s">
+        <v>4722</v>
+      </c>
+      <c r="P807" s="73" t="s">
+        <v>4723</v>
+      </c>
+      <c r="Q807" s="73" t="s">
+        <v>4724</v>
+      </c>
+      <c r="R807" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="S807" s="74" t="s">
         <v>3410</v>
       </c>
     </row>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4BAA51-E6ED-2649-8F43-CBBDCFAB1DFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E80889-03E6-B643-9F09-8039E63DD1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18362,12 +18362,31 @@
         </r>
       </text>
     </comment>
+    <comment ref="I809" authorId="0" shapeId="0" xr:uid="{1C259AC5-0820-6A4B-A192-569DF4414AD1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>애랑: 주다온
+옹녀: 김초하
+은애: 한보라
+프린스 차밍: 김이담
+그림: 최반석
+이름없는 등장인물(산삼): 김현기</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12124" uniqueCount="4729">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12139" uniqueCount="4735">
   <si>
     <t>시즌</t>
   </si>
@@ -32554,6 +32573,24 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.j529czovo7ig</t>
+  </si>
+  <si>
+    <t>주다온, 김초하, 한보라, 김이담, 최반석, 김현기</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1M8WQvXp1LVebzOgKSe6FP67AWNwdSRuC/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1TAjtPFhkZiJG_RNAjJZGcvgeBfD6PgBJ/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224433404612</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.vvrqfrs439ne</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/305847</t>
   </si>
 </sst>
 </file>
@@ -32796,7 +32833,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -32989,6 +33026,36 @@
     </xf>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -33931,7 +33998,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S808" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S809" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -34258,7 +34325,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V808"/>
+  <dimension ref="A1:V809"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -83365,6 +83432,65 @@
         <v>3408</v>
       </c>
     </row>
+    <row r="809" spans="1:19" ht="17" customHeight="1">
+      <c r="A809" s="65">
+        <v>808</v>
+      </c>
+      <c r="B809" s="66">
+        <v>46301</v>
+      </c>
+      <c r="C809" s="67">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D809" s="68" t="s">
+        <v>58</v>
+      </c>
+      <c r="E809" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F809" s="68" t="s">
+        <v>25</v>
+      </c>
+      <c r="G809" s="69" t="s">
+        <v>4692</v>
+      </c>
+      <c r="H809" s="68" t="s">
+        <v>358</v>
+      </c>
+      <c r="I809" s="70" t="s">
+        <v>4729</v>
+      </c>
+      <c r="J809" s="71">
+        <v>0</v>
+      </c>
+      <c r="K809" s="72" t="s">
+        <v>14</v>
+      </c>
+      <c r="L809" s="73" t="s">
+        <v>4730</v>
+      </c>
+      <c r="M809" s="52" t="s">
+        <v>4731</v>
+      </c>
+      <c r="N809" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O809" s="73" t="s">
+        <v>4732</v>
+      </c>
+      <c r="P809" s="73" t="s">
+        <v>4733</v>
+      </c>
+      <c r="Q809" s="73" t="s">
+        <v>4734</v>
+      </c>
+      <c r="R809" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="S809" s="74" t="s">
+        <v>3409</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E80889-03E6-B643-9F09-8039E63DD1F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46760A68-5FA8-6B46-90AB-909C4DDE40E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18381,12 +18381,30 @@
         </r>
       </text>
     </comment>
+    <comment ref="I810" authorId="0" shapeId="0" xr:uid="{FE0450DA-BC1E-CC45-A168-DF823C39D355}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>레오: 김준우
+아트: 주이진
+루퍼트: 지상윤
+케넷: 이주원
+데이지: 장수지</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12139" uniqueCount="4735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12154" uniqueCount="4739">
   <si>
     <t>시즌</t>
   </si>
@@ -32591,6 +32609,18 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/305847</t>
+  </si>
+  <si>
+    <t>김준우, 주이진, 지상윤, 이주원, 장수지</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1y2dT6hi3c_3tKkYRWYiuhxRQ7yzhLyAc/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224437253658</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.1yhgw1abig44</t>
   </si>
 </sst>
 </file>
@@ -33998,7 +34028,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S809" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S810" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -34325,7 +34355,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V809"/>
+  <dimension ref="A1:V810"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -83433,40 +83463,40 @@
       </c>
     </row>
     <row r="809" spans="1:19" ht="17" customHeight="1">
-      <c r="A809" s="65">
+      <c r="A809" s="59">
         <v>808</v>
       </c>
-      <c r="B809" s="66">
+      <c r="B809" s="60">
         <v>46301</v>
       </c>
-      <c r="C809" s="67">
+      <c r="C809" s="61">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D809" s="68" t="s">
+      <c r="D809" s="59" t="s">
         <v>58</v>
       </c>
-      <c r="E809" s="68" t="s">
+      <c r="E809" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="F809" s="68" t="s">
+      <c r="F809" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="G809" s="69" t="s">
+      <c r="G809" s="62" t="s">
         <v>4692</v>
       </c>
-      <c r="H809" s="68" t="s">
+      <c r="H809" s="59" t="s">
         <v>358</v>
       </c>
-      <c r="I809" s="70" t="s">
+      <c r="I809" s="63" t="s">
         <v>4729</v>
       </c>
-      <c r="J809" s="71">
+      <c r="J809" s="54">
         <v>0</v>
       </c>
-      <c r="K809" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="L809" s="73" t="s">
+      <c r="K809" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="L809" s="51" t="s">
         <v>4730</v>
       </c>
       <c r="M809" s="52" t="s">
@@ -83475,20 +83505,79 @@
       <c r="N809" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="O809" s="73" t="s">
+      <c r="O809" s="51" t="s">
         <v>4732</v>
       </c>
-      <c r="P809" s="73" t="s">
+      <c r="P809" s="51" t="s">
         <v>4733</v>
       </c>
-      <c r="Q809" s="73" t="s">
+      <c r="Q809" s="51" t="s">
         <v>4734</v>
       </c>
-      <c r="R809" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="S809" s="74" t="s">
+      <c r="R809" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="S809" s="47" t="s">
         <v>3409</v>
+      </c>
+    </row>
+    <row r="810" spans="1:19" ht="17" customHeight="1">
+      <c r="A810" s="65">
+        <v>809</v>
+      </c>
+      <c r="B810" s="66">
+        <v>46304</v>
+      </c>
+      <c r="C810" s="67">
+        <v>0.625</v>
+      </c>
+      <c r="D810" s="68" t="s">
+        <v>4280</v>
+      </c>
+      <c r="E810" s="68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F810" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G810" s="69" t="s">
+        <v>4699</v>
+      </c>
+      <c r="H810" s="68" t="s">
+        <v>362</v>
+      </c>
+      <c r="I810" s="70" t="s">
+        <v>4735</v>
+      </c>
+      <c r="J810" s="71">
+        <v>22500</v>
+      </c>
+      <c r="K810" s="72" t="s">
+        <v>4282</v>
+      </c>
+      <c r="L810" s="73" t="s">
+        <v>4736</v>
+      </c>
+      <c r="M810" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="N810" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O810" s="73" t="s">
+        <v>4737</v>
+      </c>
+      <c r="P810" s="73" t="s">
+        <v>4738</v>
+      </c>
+      <c r="Q810" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R810" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="S810" s="74" t="s">
+        <v>3408</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46760A68-5FA8-6B46-90AB-909C4DDE40E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B462C5-7209-4149-B9F5-73F7AF0594AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18399,12 +18399,209 @@
         </r>
       </text>
     </comment>
+    <comment ref="I811" authorId="0" shapeId="0" xr:uid="{330ED0A9-BBDF-6C4A-A5FB-9A709E740886}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>레오: 우지한
+아트: 주이진
+루퍼트: 지상윤
+케넷: 정이운
+데이지: 김한나</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I812" authorId="0" shapeId="0" xr:uid="{C0E90EB4-344D-BD42-B62C-3E204EAE5C48}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>레오</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김준우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주이진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루퍼트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>지상윤</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>케넷</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정이운</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>데이지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>장수지</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12154" uniqueCount="4739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12184" uniqueCount="4747">
   <si>
     <t>시즌</t>
   </si>
@@ -32621,6 +32818,30 @@
   </si>
   <si>
     <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.1yhgw1abig44</t>
+  </si>
+  <si>
+    <t>김준우, 주이진, 지상윤, 정이운, 장수지</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/15kaJ20ZG5H6Y3nbJNGlPmBgwNqg2N63I/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224442458521</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.kcfi4oqeqbk</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Mvg288YALuDuwH92MSlBDN0ChM7qhD-6/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224442461201</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.yp9x96wgncft</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/306536</t>
   </si>
 </sst>
 </file>
@@ -32863,7 +33084,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -33056,6 +33277,36 @@
     </xf>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -34028,7 +34279,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S810" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S812" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -34355,7 +34606,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V810"/>
+  <dimension ref="A1:V812"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -83522,40 +83773,40 @@
       </c>
     </row>
     <row r="810" spans="1:19" ht="17" customHeight="1">
-      <c r="A810" s="65">
+      <c r="A810" s="59">
         <v>809</v>
       </c>
-      <c r="B810" s="66">
+      <c r="B810" s="60">
         <v>46304</v>
       </c>
-      <c r="C810" s="67">
+      <c r="C810" s="61">
         <v>0.625</v>
       </c>
-      <c r="D810" s="68" t="s">
+      <c r="D810" s="59" t="s">
         <v>4280</v>
       </c>
-      <c r="E810" s="68" t="s">
+      <c r="E810" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="F810" s="68" t="s">
+      <c r="F810" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="G810" s="69" t="s">
+      <c r="G810" s="62" t="s">
         <v>4699</v>
       </c>
-      <c r="H810" s="68" t="s">
+      <c r="H810" s="59" t="s">
         <v>362</v>
       </c>
-      <c r="I810" s="70" t="s">
+      <c r="I810" s="63" t="s">
         <v>4735</v>
       </c>
-      <c r="J810" s="71">
+      <c r="J810" s="54">
         <v>22500</v>
       </c>
-      <c r="K810" s="72" t="s">
+      <c r="K810" s="50" t="s">
         <v>4282</v>
       </c>
-      <c r="L810" s="73" t="s">
+      <c r="L810" s="51" t="s">
         <v>4736</v>
       </c>
       <c r="M810" s="52" t="s">
@@ -83564,20 +83815,138 @@
       <c r="N810" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="O810" s="73" t="s">
+      <c r="O810" s="51" t="s">
         <v>4737</v>
       </c>
-      <c r="P810" s="73" t="s">
+      <c r="P810" s="51" t="s">
         <v>4738</v>
       </c>
-      <c r="Q810" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R810" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="S810" s="74" t="s">
+      <c r="Q810" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="R810" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="S810" s="47" t="s">
         <v>3408</v>
+      </c>
+    </row>
+    <row r="811" spans="1:19" ht="17" customHeight="1">
+      <c r="A811" s="65">
+        <v>810</v>
+      </c>
+      <c r="B811" s="66">
+        <v>46309</v>
+      </c>
+      <c r="C811" s="67">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D811" s="68" t="s">
+        <v>4280</v>
+      </c>
+      <c r="E811" s="68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F811" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G811" s="69" t="s">
+        <v>4699</v>
+      </c>
+      <c r="H811" s="68" t="s">
+        <v>363</v>
+      </c>
+      <c r="I811" s="70" t="s">
+        <v>4716</v>
+      </c>
+      <c r="J811" s="71">
+        <v>13000</v>
+      </c>
+      <c r="K811" s="72" t="s">
+        <v>4282</v>
+      </c>
+      <c r="L811" s="73" t="s">
+        <v>4740</v>
+      </c>
+      <c r="M811" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N811" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O811" s="73" t="s">
+        <v>4741</v>
+      </c>
+      <c r="P811" s="73" t="s">
+        <v>4742</v>
+      </c>
+      <c r="Q811" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R811" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="S811" s="74" t="s">
+        <v>3408</v>
+      </c>
+    </row>
+    <row r="812" spans="1:19" ht="17" customHeight="1">
+      <c r="A812" s="75">
+        <v>811</v>
+      </c>
+      <c r="B812" s="76">
+        <v>46309</v>
+      </c>
+      <c r="C812" s="77">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D812" s="78" t="s">
+        <v>4280</v>
+      </c>
+      <c r="E812" s="78" t="s">
+        <v>29</v>
+      </c>
+      <c r="F812" s="78" t="s">
+        <v>30</v>
+      </c>
+      <c r="G812" s="79" t="s">
+        <v>4699</v>
+      </c>
+      <c r="H812" s="78" t="s">
+        <v>364</v>
+      </c>
+      <c r="I812" s="80" t="s">
+        <v>4739</v>
+      </c>
+      <c r="J812" s="81">
+        <v>18500</v>
+      </c>
+      <c r="K812" s="82" t="s">
+        <v>4282</v>
+      </c>
+      <c r="L812" s="83" t="s">
+        <v>4743</v>
+      </c>
+      <c r="M812" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="N812" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="O812" s="83" t="s">
+        <v>4744</v>
+      </c>
+      <c r="P812" s="83" t="s">
+        <v>4745</v>
+      </c>
+      <c r="Q812" s="83" t="s">
+        <v>4746</v>
+      </c>
+      <c r="R812" s="83" t="s">
+        <v>14</v>
+      </c>
+      <c r="S812" s="84" t="s">
+        <v>3410</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B462C5-7209-4149-B9F5-73F7AF0594AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D0FB2E-7CA7-5F40-9840-E5F283D41CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
@@ -18596,12 +18596,245 @@
         </r>
       </text>
     </comment>
+    <comment ref="I813" authorId="0" shapeId="0" xr:uid="{65E9EF49-FE97-DD44-8EE3-F5024FCF6533}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>르네</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>갈리마르</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>안재영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>송</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>릴링</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김바다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>핑커튼</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>장재웅</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아녜스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> / </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>친</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>전하영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>툴롱</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김승용</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12184" uniqueCount="4747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12199" uniqueCount="4754">
   <si>
     <t>시즌</t>
   </si>
@@ -32842,6 +33075,27 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/306536</t>
+  </si>
+  <si>
+    <t>엠. 버터플라이</t>
+  </si>
+  <si>
+    <t>안재영, 김바다, 장재웅, 전하영, 김승용</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/132jZ4ZIPqV06lFwaisnAKRelfO4MIe8A/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1iyEdokFF3pER0G3QxYHUpe_emVl4dp4y/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224445024616</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.nu6x3fj8296a</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/306779</t>
   </si>
 </sst>
 </file>
@@ -33084,7 +33338,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -33277,36 +33531,6 @@
     </xf>
     <xf numFmtId="166" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -34279,7 +34503,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S812" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S813" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -34606,7 +34830,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V812"/>
+  <dimension ref="A1:V813"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -83832,40 +84056,40 @@
       </c>
     </row>
     <row r="811" spans="1:19" ht="17" customHeight="1">
-      <c r="A811" s="65">
+      <c r="A811" s="36">
         <v>810</v>
       </c>
-      <c r="B811" s="66">
+      <c r="B811" s="37">
         <v>46309</v>
       </c>
-      <c r="C811" s="67">
+      <c r="C811" s="38">
         <v>0.66666666666666663</v>
       </c>
-      <c r="D811" s="68" t="s">
+      <c r="D811" s="36" t="s">
         <v>4280</v>
       </c>
-      <c r="E811" s="68" t="s">
+      <c r="E811" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="F811" s="68" t="s">
+      <c r="F811" s="36" t="s">
         <v>30</v>
       </c>
-      <c r="G811" s="69" t="s">
+      <c r="G811" s="39" t="s">
         <v>4699</v>
       </c>
-      <c r="H811" s="68" t="s">
+      <c r="H811" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="I811" s="70" t="s">
+      <c r="I811" s="56" t="s">
         <v>4716</v>
       </c>
-      <c r="J811" s="71">
+      <c r="J811" s="55">
         <v>13000</v>
       </c>
-      <c r="K811" s="72" t="s">
+      <c r="K811" s="46" t="s">
         <v>4282</v>
       </c>
-      <c r="L811" s="73" t="s">
+      <c r="L811" s="40" t="s">
         <v>4740</v>
       </c>
       <c r="M811" s="15" t="s">
@@ -83874,57 +84098,57 @@
       <c r="N811" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="O811" s="73" t="s">
+      <c r="O811" s="40" t="s">
         <v>4741</v>
       </c>
-      <c r="P811" s="73" t="s">
+      <c r="P811" s="40" t="s">
         <v>4742</v>
       </c>
-      <c r="Q811" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="R811" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="S811" s="74" t="s">
+      <c r="Q811" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="R811" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="S811" s="47" t="s">
         <v>3408</v>
       </c>
     </row>
     <row r="812" spans="1:19" ht="17" customHeight="1">
-      <c r="A812" s="75">
+      <c r="A812" s="59">
         <v>811</v>
       </c>
-      <c r="B812" s="76">
+      <c r="B812" s="60">
         <v>46309</v>
       </c>
-      <c r="C812" s="77">
+      <c r="C812" s="61">
         <v>0.83333333333333337</v>
       </c>
-      <c r="D812" s="78" t="s">
+      <c r="D812" s="59" t="s">
         <v>4280</v>
       </c>
-      <c r="E812" s="78" t="s">
+      <c r="E812" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="F812" s="78" t="s">
+      <c r="F812" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="G812" s="79" t="s">
+      <c r="G812" s="62" t="s">
         <v>4699</v>
       </c>
-      <c r="H812" s="78" t="s">
+      <c r="H812" s="59" t="s">
         <v>364</v>
       </c>
-      <c r="I812" s="80" t="s">
+      <c r="I812" s="63" t="s">
         <v>4739</v>
       </c>
-      <c r="J812" s="81">
+      <c r="J812" s="54">
         <v>18500</v>
       </c>
-      <c r="K812" s="82" t="s">
+      <c r="K812" s="50" t="s">
         <v>4282</v>
       </c>
-      <c r="L812" s="83" t="s">
+      <c r="L812" s="51" t="s">
         <v>4743</v>
       </c>
       <c r="M812" s="52" t="s">
@@ -83933,20 +84157,79 @@
       <c r="N812" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="O812" s="83" t="s">
+      <c r="O812" s="51" t="s">
         <v>4744</v>
       </c>
-      <c r="P812" s="83" t="s">
+      <c r="P812" s="51" t="s">
         <v>4745</v>
       </c>
-      <c r="Q812" s="83" t="s">
+      <c r="Q812" s="51" t="s">
         <v>4746</v>
       </c>
-      <c r="R812" s="83" t="s">
-        <v>14</v>
-      </c>
-      <c r="S812" s="84" t="s">
+      <c r="R812" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="S812" s="47" t="s">
         <v>3410</v>
+      </c>
+    </row>
+    <row r="813" spans="1:19" ht="17" customHeight="1">
+      <c r="A813" s="65">
+        <v>812</v>
+      </c>
+      <c r="B813" s="66">
+        <v>46312</v>
+      </c>
+      <c r="C813" s="67">
+        <v>0.625</v>
+      </c>
+      <c r="D813" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="E813" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F813" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="G813" s="69" t="s">
+        <v>4747</v>
+      </c>
+      <c r="H813" s="68" t="s">
+        <v>357</v>
+      </c>
+      <c r="I813" s="70" t="s">
+        <v>4748</v>
+      </c>
+      <c r="J813" s="71">
+        <v>16000</v>
+      </c>
+      <c r="K813" s="72" t="s">
+        <v>39</v>
+      </c>
+      <c r="L813" s="73" t="s">
+        <v>4749</v>
+      </c>
+      <c r="M813" s="52" t="s">
+        <v>4750</v>
+      </c>
+      <c r="N813" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O813" s="73" t="s">
+        <v>4751</v>
+      </c>
+      <c r="P813" s="73" t="s">
+        <v>4752</v>
+      </c>
+      <c r="Q813" s="73" t="s">
+        <v>4753</v>
+      </c>
+      <c r="R813" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="S813" s="74" t="s">
+        <v>3408</v>
       </c>
     </row>
   </sheetData>

--- a/RawData.xlsx
+++ b/RawData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/js/myenv/test_1/SailingSnails/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4D0FB2E-7CA7-5F40-9840-E5F283D41CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C03DF6-5817-1A4A-8E57-62924038E4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="14400" windowHeight="17400" xr2:uid="{A9EF6BCE-6681-424E-A755-53C4540C4A5C}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -18596,11 +18596,46 @@
         </r>
       </text>
     </comment>
-    <comment ref="I813" authorId="0" shapeId="0" xr:uid="{65E9EF49-FE97-DD44-8EE3-F5024FCF6533}">
+    <comment ref="I813" authorId="0" shapeId="0" xr:uid="{C5BB2798-2EA5-264E-BEF3-388E27EF409F}">
       <text>
         <r>
           <rPr>
             <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>르네 갈리마르: 안재영
+송 릴링: 김바다
+핑커튼: 장재웅
+아녜스 / 친: 전하영
+툴롱: 김승용</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I814" authorId="0" shapeId="0" xr:uid="{62474C43-57BA-8C42-8B85-CEC3670D98FB}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>비지터: 고상호
+맨: 이창용
+우먼: 김리
+멀티: 정종환, 방가희</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I815" authorId="0" shapeId="0" xr:uid="{4C6A2AF7-1082-824C-A42B-059382877EEC}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="Calibri"/>
             <family val="2"/>
@@ -18641,7 +18676,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>안재영</t>
+          <t>주민진</t>
         </r>
         <r>
           <rPr>
@@ -18696,7 +18731,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>김바다</t>
+          <t>유태율</t>
         </r>
         <r>
           <rPr>
@@ -18733,7 +18768,7 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
-          <t>장재웅</t>
+          <t>남민우</t>
         </r>
         <r>
           <rPr>
@@ -18825,7 +18860,598 @@
             <rFont val="Calibri"/>
             <family val="2"/>
           </rPr>
+          <t>황만익</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I816" authorId="0" shapeId="0" xr:uid="{10D6AC28-827F-0640-88E7-4E8EB118BDB0}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>레오</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김준우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>주이진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루퍼트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>지상윤</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>케넷</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정이운</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>데이지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김한나</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I817" authorId="0" shapeId="0" xr:uid="{97C26B62-F3CE-C643-858F-4AB88537F4A9}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>르네</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>갈리마르</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>유현석</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>송</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>릴링</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>김바다</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>핑커튼</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>남민우</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아녜스</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> / </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>친</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>전하영</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>툴롱</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
           <t>김승용</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I818" authorId="0" shapeId="0" xr:uid="{42FB014E-B022-2640-804D-D35DAA4F2C32}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>레오</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>차유진</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>아트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>백민서</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>루퍼트</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>서동근</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>케넷</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>정이운</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>데이지</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">: </t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+          </rPr>
+          <t>장수지</t>
         </r>
       </text>
     </comment>
@@ -18834,7 +19460,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12199" uniqueCount="4754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12274" uniqueCount="4780">
   <si>
     <t>시즌</t>
   </si>
@@ -33096,6 +33722,84 @@
   </si>
   <si>
     <t>https://m.dcinside.com/mini/musicalplay/306779</t>
+  </si>
+  <si>
+    <t>고상호, 이창용, 김리, 정종환, 방가희</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1_AV_fDsfocwBSxQBwTcLNTDZoo8s8bhc/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224446554482</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.g4xswp85sjcb</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/306873</t>
+  </si>
+  <si>
+    <t>주민진, 유태율, 남민우, 전하영, 황만익</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1RC4aKWstIfVjFyxU4LFoIQXCRjGHzJhb/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/10Enci2x-pWSHXmtT9JGltwMpcw-pIIC9/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1Tf-WLOq8H8bpNCPPOLOzBRBAuuVb7Sk_/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224447845746</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.uolqvsw3kyv4</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/306953</t>
+  </si>
+  <si>
+    <t>김준우, 주이진, 지상윤, 정이운, 김한나</t>
+  </si>
+  <si>
+    <t>유현석, 김바다, 남민우, 전하영, 김승용</t>
+  </si>
+  <si>
+    <t>차유진, 백민서, 서동근, 정이운, 장수지</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1EBMnAlqKHVFf1QBTdWkg9ORCTBfdFvF-/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224451341018</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.9in1rylecyxy</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1HCSt2M3vKRCB2deI98SXiWQW0A1jSNAd/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1ui8DZiDDu5W5wDzcwDNM803asVrcyKaN/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224451343987</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.73dpgt2cm141</t>
+  </si>
+  <si>
+    <t>https://m.dcinside.com/mini/musicalplay/307103</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1V4QnNx7Hj_SIGtShmHOUH4fMO5qIfRHe/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://blog.naver.com/playnmu/224451349863</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/document/d/1CSxTzEcx4Fgr6bF_h2g9BxJYFypmYPtv_Gc02-qe1ss/edit?tab=t.0#heading=h.w0tn9p5unqfh</t>
   </si>
 </sst>
 </file>
@@ -33532,34 +34236,34 @@
     <xf numFmtId="166" fontId="2" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -34503,7 +35207,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S813" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4CF1CA70-B8DA-4ADA-9B22-302960093E18}" name="전체" displayName="전체" ref="A1:S818" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R706">
     <sortCondition ref="B200:B706"/>
   </sortState>
@@ -34830,7 +35534,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCCB8FC5-3A29-48CA-894D-6639F6E020DC}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V813"/>
+  <dimension ref="A1:V818"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="17" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.6640625" style="3" customWidth="1"/>
@@ -84174,40 +84878,40 @@
       </c>
     </row>
     <row r="813" spans="1:19" ht="17" customHeight="1">
-      <c r="A813" s="65">
+      <c r="A813" s="59">
         <v>812</v>
       </c>
-      <c r="B813" s="66">
+      <c r="B813" s="60">
         <v>46312</v>
       </c>
-      <c r="C813" s="67">
+      <c r="C813" s="61">
         <v>0.625</v>
       </c>
-      <c r="D813" s="68" t="s">
+      <c r="D813" s="59" t="s">
         <v>174</v>
       </c>
-      <c r="E813" s="68" t="s">
+      <c r="E813" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="F813" s="68" t="s">
+      <c r="F813" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="G813" s="69" t="s">
+      <c r="G813" s="62" t="s">
         <v>4747</v>
       </c>
-      <c r="H813" s="68" t="s">
+      <c r="H813" s="59" t="s">
         <v>357</v>
       </c>
-      <c r="I813" s="70" t="s">
+      <c r="I813" s="63" t="s">
         <v>4748</v>
       </c>
-      <c r="J813" s="71">
+      <c r="J813" s="54">
         <v>16000</v>
       </c>
-      <c r="K813" s="72" t="s">
+      <c r="K813" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="L813" s="73" t="s">
+      <c r="L813" s="51" t="s">
         <v>4749</v>
       </c>
       <c r="M813" s="52" t="s">
@@ -84216,20 +84920,315 @@
       <c r="N813" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="O813" s="73" t="s">
+      <c r="O813" s="51" t="s">
         <v>4751</v>
       </c>
-      <c r="P813" s="73" t="s">
+      <c r="P813" s="51" t="s">
         <v>4752</v>
       </c>
-      <c r="Q813" s="73" t="s">
+      <c r="Q813" s="51" t="s">
         <v>4753</v>
       </c>
-      <c r="R813" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="S813" s="74" t="s">
+      <c r="R813" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="S813" s="47" t="s">
         <v>3408</v>
+      </c>
+    </row>
+    <row r="814" spans="1:19" ht="17" customHeight="1">
+      <c r="A814" s="59">
+        <v>813</v>
+      </c>
+      <c r="B814" s="60">
+        <v>46313</v>
+      </c>
+      <c r="C814" s="61">
+        <v>0.75</v>
+      </c>
+      <c r="D814" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="E814" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="F814" s="59" t="s">
+        <v>7</v>
+      </c>
+      <c r="G814" s="62" t="s">
+        <v>123</v>
+      </c>
+      <c r="H814" s="59" t="s">
+        <v>357</v>
+      </c>
+      <c r="I814" s="63" t="s">
+        <v>4754</v>
+      </c>
+      <c r="J814" s="54">
+        <v>17500</v>
+      </c>
+      <c r="K814" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="L814" s="51" t="s">
+        <v>4755</v>
+      </c>
+      <c r="M814" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="N814" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O814" s="51" t="s">
+        <v>4756</v>
+      </c>
+      <c r="P814" s="51" t="s">
+        <v>4757</v>
+      </c>
+      <c r="Q814" s="51" t="s">
+        <v>4758</v>
+      </c>
+      <c r="R814" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="S814" s="47" t="s">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="815" spans="1:19" ht="17" customHeight="1">
+      <c r="A815" s="59">
+        <v>814</v>
+      </c>
+      <c r="B815" s="60">
+        <v>46314</v>
+      </c>
+      <c r="C815" s="61">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D815" s="59" t="s">
+        <v>174</v>
+      </c>
+      <c r="E815" s="59" t="s">
+        <v>12</v>
+      </c>
+      <c r="F815" s="59" t="s">
+        <v>25</v>
+      </c>
+      <c r="G815" s="62" t="s">
+        <v>4747</v>
+      </c>
+      <c r="H815" s="59" t="s">
+        <v>358</v>
+      </c>
+      <c r="I815" s="63" t="s">
+        <v>4759</v>
+      </c>
+      <c r="J815" s="54">
+        <v>0</v>
+      </c>
+      <c r="K815" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="L815" s="51" t="s">
+        <v>4760</v>
+      </c>
+      <c r="M815" s="52" t="s">
+        <v>4761</v>
+      </c>
+      <c r="N815" s="52" t="s">
+        <v>4762</v>
+      </c>
+      <c r="O815" s="51" t="s">
+        <v>4763</v>
+      </c>
+      <c r="P815" s="51" t="s">
+        <v>4764</v>
+      </c>
+      <c r="Q815" s="51" t="s">
+        <v>4765</v>
+      </c>
+      <c r="R815" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="S815" s="47" t="s">
+        <v>3410</v>
+      </c>
+    </row>
+    <row r="816" spans="1:19" ht="17" customHeight="1">
+      <c r="A816" s="65">
+        <v>815</v>
+      </c>
+      <c r="B816" s="66">
+        <v>46316</v>
+      </c>
+      <c r="C816" s="67">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D816" s="68" t="s">
+        <v>4280</v>
+      </c>
+      <c r="E816" s="68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F816" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G816" s="69" t="s">
+        <v>4699</v>
+      </c>
+      <c r="H816" s="68" t="s">
+        <v>365</v>
+      </c>
+      <c r="I816" s="70" t="s">
+        <v>4766</v>
+      </c>
+      <c r="J816" s="71">
+        <v>17087</v>
+      </c>
+      <c r="K816" s="72" t="s">
+        <v>4282</v>
+      </c>
+      <c r="L816" s="73" t="s">
+        <v>4769</v>
+      </c>
+      <c r="M816" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N816" s="52" t="s">
+        <v>14</v>
+      </c>
+      <c r="O816" s="73" t="s">
+        <v>4770</v>
+      </c>
+      <c r="P816" s="73" t="s">
+        <v>4771</v>
+      </c>
+      <c r="Q816" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R816" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="S816" s="74" t="s">
+        <v>3408</v>
+      </c>
+    </row>
+    <row r="817" spans="1:19" ht="17" customHeight="1">
+      <c r="A817" s="65">
+        <v>816</v>
+      </c>
+      <c r="B817" s="66">
+        <v>46316</v>
+      </c>
+      <c r="C817" s="67">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D817" s="68" t="s">
+        <v>174</v>
+      </c>
+      <c r="E817" s="68" t="s">
+        <v>12</v>
+      </c>
+      <c r="F817" s="68" t="s">
+        <v>7</v>
+      </c>
+      <c r="G817" s="69" t="s">
+        <v>4747</v>
+      </c>
+      <c r="H817" s="68" t="s">
+        <v>359</v>
+      </c>
+      <c r="I817" s="70" t="s">
+        <v>4767</v>
+      </c>
+      <c r="J817" s="71">
+        <v>0</v>
+      </c>
+      <c r="K817" s="72" t="s">
+        <v>39</v>
+      </c>
+      <c r="L817" s="73" t="s">
+        <v>4772</v>
+      </c>
+      <c r="M817" s="15" t="s">
+        <v>4773</v>
+      </c>
+      <c r="N817" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="O817" s="73" t="s">
+        <v>4774</v>
+      </c>
+      <c r="P817" s="73" t="s">
+        <v>4775</v>
+      </c>
+      <c r="Q817" s="73" t="s">
+        <v>4776</v>
+      </c>
+      <c r="R817" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="S817" s="74" t="s">
+        <v>3411</v>
+      </c>
+    </row>
+    <row r="818" spans="1:19" ht="17" customHeight="1">
+      <c r="A818" s="65">
+        <v>817</v>
+      </c>
+      <c r="B818" s="66">
+        <v>46317</v>
+      </c>
+      <c r="C818" s="67">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="D818" s="68" t="s">
+        <v>4280</v>
+      </c>
+      <c r="E818" s="68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F818" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="G818" s="69" t="s">
+        <v>4699</v>
+      </c>
+      <c r="H818" s="68" t="s">
+        <v>366</v>
+      </c>
+      <c r="I818" s="70" t="s">
+        <v>4768</v>
+      </c>
+      <c r="J818" s="71">
+        <v>11000</v>
+      </c>
+      <c r="K818" s="72" t="s">
+        <v>4282</v>
+      </c>
+      <c r="L818" s="73" t="s">
+        <v>4777</v>
+      </c>
+      <c r="M818" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="N818" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="O818" s="73" t="s">
+        <v>4778</v>
+      </c>
+      <c r="P818" s="73" t="s">
+        <v>4779</v>
+      </c>
+      <c r="Q818" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="R818" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="S818" s="74" t="s">
+        <v>3412</v>
       </c>
     </row>
   </sheetData>
